--- a/Trankit/Trankit_new_words.xlsx
+++ b/Trankit/Trankit_new_words.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Diplomovka\Trankit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13D64BE-F9D0-4F76-BB8E-ED343C70167F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F474950-1947-4E56-B051-9A71C445AC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$1200</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -349,9 +352,6 @@
     <t>:</t>
   </si>
   <si>
-    <t>r</t>
-  </si>
-  <si>
     <t>kde</t>
   </si>
   <si>
@@ -2423,6 +2423,9 @@
   </si>
   <si>
     <t>Výchovno-vzdelávací</t>
+  </si>
+  <si>
+    <t>:r</t>
   </si>
 </sst>
 </file>
@@ -5508,10 +5511,10 @@
         <v>29</v>
       </c>
       <c r="G94" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H94" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I94">
         <v>5</v>
@@ -5548,7 +5551,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" t="s">
         <v>40</v>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
         <v>10</v>
@@ -5635,7 +5638,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B99" t="s">
         <v>21</v>
@@ -5693,7 +5696,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B103" t="s">
         <v>21</v>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B105" t="s">
         <v>21</v>
@@ -5867,7 +5870,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B107" t="s">
         <v>21</v>
@@ -5925,7 +5928,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B109" t="s">
         <v>25</v>
@@ -5954,7 +5957,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110" t="s">
         <v>10</v>
@@ -5983,7 +5986,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B111" t="s">
         <v>21</v>
@@ -6041,7 +6044,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B113" t="s">
         <v>56</v>
@@ -6070,7 +6073,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B114" t="s">
         <v>21</v>
@@ -6128,7 +6131,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B116" t="s">
         <v>18</v>
@@ -6157,7 +6160,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
         <v>40</v>
@@ -6186,7 +6189,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B118" t="s">
         <v>10</v>
@@ -6215,7 +6218,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B119" t="s">
         <v>56</v>
@@ -6244,7 +6247,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B120" t="s">
         <v>21</v>
@@ -6302,7 +6305,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B122" t="s">
         <v>10</v>
@@ -6360,7 +6363,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124" t="s">
         <v>21</v>
@@ -6418,7 +6421,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B126" t="s">
         <v>21</v>
@@ -6476,7 +6479,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B128" t="s">
         <v>55</v>
@@ -6534,7 +6537,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B130" t="s">
         <v>10</v>
@@ -6592,7 +6595,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B132" t="s">
         <v>40</v>
@@ -6650,7 +6653,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B134" t="s">
         <v>10</v>
@@ -6679,7 +6682,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135" t="s">
         <v>21</v>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136" t="s">
         <v>27</v>
@@ -6737,7 +6740,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" t="s">
         <v>21</v>
@@ -6795,7 +6798,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B139" t="s">
         <v>18</v>
@@ -6853,7 +6856,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
         <v>40</v>
@@ -6882,7 +6885,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B142" t="s">
         <v>21</v>
@@ -6911,7 +6914,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
         <v>40</v>
@@ -6940,7 +6943,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
         <v>10</v>
@@ -6969,7 +6972,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B145" t="s">
         <v>56</v>
@@ -6998,7 +7001,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B146" t="s">
         <v>21</v>
@@ -7056,13 +7059,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B148" t="s">
         <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D148" t="s">
         <v>16</v>
@@ -7114,13 +7117,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>144</v>
+      </c>
+      <c r="B150" t="s">
+        <v>21</v>
+      </c>
+      <c r="C150" t="s">
         <v>145</v>
-      </c>
-      <c r="B150" t="s">
-        <v>21</v>
-      </c>
-      <c r="C150" t="s">
-        <v>146</v>
       </c>
       <c r="D150" t="s">
         <v>31</v>
@@ -7143,7 +7146,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B151" t="s">
         <v>21</v>
@@ -7172,7 +7175,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B152" t="s">
         <v>10</v>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B154" t="s">
         <v>40</v>
@@ -7259,7 +7262,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B155" t="s">
         <v>40</v>
@@ -7288,7 +7291,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B156" t="s">
         <v>10</v>
@@ -7346,7 +7349,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B158" t="s">
         <v>10</v>
@@ -7433,13 +7436,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B161" t="s">
         <v>55</v>
       </c>
       <c r="C161" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D161" t="s">
         <v>35</v>
@@ -7462,7 +7465,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B162" t="s">
         <v>21</v>
@@ -7491,7 +7494,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B163" t="s">
         <v>40</v>
@@ -7520,7 +7523,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B164" t="s">
         <v>10</v>
@@ -7549,7 +7552,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B165" t="s">
         <v>56</v>
@@ -7578,7 +7581,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B166" t="s">
         <v>56</v>
@@ -7607,7 +7610,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B167" t="s">
         <v>21</v>
@@ -7665,7 +7668,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B169" t="s">
         <v>56</v>
@@ -7694,7 +7697,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B170" t="s">
         <v>21</v>
@@ -7752,7 +7755,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B172" t="s">
         <v>10</v>
@@ -7810,7 +7813,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B174" t="s">
         <v>86</v>
@@ -7839,7 +7842,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B175" t="s">
         <v>10</v>
@@ -7897,13 +7900,13 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B177" t="s">
         <v>25</v>
       </c>
       <c r="C177" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D177" t="s">
         <v>16</v>
@@ -7984,7 +7987,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B180" t="s">
         <v>10</v>
@@ -8013,7 +8016,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B181" t="s">
         <v>21</v>
@@ -8042,7 +8045,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B182" t="s">
         <v>27</v>
@@ -8071,7 +8074,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B183" t="s">
         <v>40</v>
@@ -8100,7 +8103,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B184" t="s">
         <v>56</v>
@@ -8129,7 +8132,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B185" t="s">
         <v>21</v>
@@ -8187,7 +8190,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B187" t="s">
         <v>56</v>
@@ -8216,7 +8219,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B188" t="s">
         <v>21</v>
@@ -8274,7 +8277,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B190" t="s">
         <v>56</v>
@@ -8303,7 +8306,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B191" t="s">
         <v>21</v>
@@ -8332,10 +8335,10 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B192" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C192" t="s">
         <v>16</v>
@@ -8419,7 +8422,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B195" t="s">
         <v>56</v>
@@ -8448,7 +8451,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B196" t="s">
         <v>21</v>
@@ -8506,7 +8509,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
@@ -8535,7 +8538,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B199" t="s">
         <v>21</v>
@@ -8564,7 +8567,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B200" t="s">
         <v>27</v>
@@ -8573,7 +8576,7 @@
         <v>28</v>
       </c>
       <c r="D200" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
@@ -8593,7 +8596,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B201" t="s">
         <v>21</v>
@@ -8608,7 +8611,7 @@
         <v>13</v>
       </c>
       <c r="F201" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G201" t="s">
         <v>16</v>
@@ -8622,7 +8625,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B202" t="s">
         <v>56</v>
@@ -8651,7 +8654,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B203" t="s">
         <v>21</v>
@@ -8738,7 +8741,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B206" t="s">
         <v>18</v>
@@ -8767,7 +8770,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B207" t="s">
         <v>10</v>
@@ -8857,7 +8860,7 @@
         <v>23</v>
       </c>
       <c r="B210" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C210" t="s">
         <v>16</v>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B214" t="s">
         <v>10</v>
@@ -9066,7 +9069,7 @@
         <v>28</v>
       </c>
       <c r="D217" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E217" t="s">
         <v>16</v>
@@ -9086,7 +9089,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B218" t="s">
         <v>40</v>
@@ -9101,7 +9104,7 @@
         <v>33</v>
       </c>
       <c r="F218" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G218" t="s">
         <v>16</v>
@@ -9115,7 +9118,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B219" t="s">
         <v>27</v>
@@ -9173,7 +9176,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B221" t="s">
         <v>21</v>
@@ -9231,7 +9234,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B223" t="s">
         <v>27</v>
@@ -9260,7 +9263,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B224" t="s">
         <v>21</v>
@@ -9289,7 +9292,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B225" t="s">
         <v>21</v>
@@ -9318,7 +9321,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B226" t="s">
         <v>40</v>
@@ -9347,7 +9350,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B227" t="s">
         <v>10</v>
@@ -9376,7 +9379,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B228" t="s">
         <v>56</v>
@@ -9405,7 +9408,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B229" t="s">
         <v>21</v>
@@ -9434,7 +9437,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B230" t="s">
         <v>21</v>
@@ -9452,10 +9455,10 @@
         <v>38</v>
       </c>
       <c r="G230" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H230" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I230">
         <v>15</v>
@@ -9463,7 +9466,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B231" t="s">
         <v>56</v>
@@ -9484,7 +9487,7 @@
         <v>69</v>
       </c>
       <c r="H231" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="I231">
         <v>15</v>
@@ -9521,7 +9524,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B233" t="s">
         <v>21</v>
@@ -9550,7 +9553,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B234" t="s">
         <v>21</v>
@@ -9568,10 +9571,10 @@
         <v>38</v>
       </c>
       <c r="G234" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H234" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I234">
         <v>15</v>
@@ -9579,7 +9582,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B235" t="s">
         <v>21</v>
@@ -9597,10 +9600,10 @@
         <v>38</v>
       </c>
       <c r="G235" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H235" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I235">
         <v>15</v>
@@ -9637,7 +9640,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B237" t="s">
         <v>86</v>
@@ -9695,7 +9698,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B239" t="s">
         <v>10</v>
@@ -9724,7 +9727,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B240" t="s">
         <v>21</v>
@@ -9753,7 +9756,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B241" t="s">
         <v>40</v>
@@ -9782,7 +9785,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B242" t="s">
         <v>21</v>
@@ -9840,7 +9843,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B244" t="s">
         <v>21</v>
@@ -9898,7 +9901,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B246" t="s">
         <v>21</v>
@@ -9927,7 +9930,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B247" t="s">
         <v>44</v>
@@ -9956,7 +9959,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B248" t="s">
         <v>21</v>
@@ -10014,7 +10017,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B250" t="s">
         <v>21</v>
@@ -10043,7 +10046,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B251" t="s">
         <v>44</v>
@@ -10072,7 +10075,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B252" t="s">
         <v>21</v>
@@ -10130,7 +10133,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B254" t="s">
         <v>10</v>
@@ -10159,7 +10162,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B255" t="s">
         <v>21</v>
@@ -10188,7 +10191,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B256" t="s">
         <v>44</v>
@@ -10217,7 +10220,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B257" t="s">
         <v>21</v>
@@ -10275,7 +10278,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B259" t="s">
         <v>10</v>
@@ -10304,7 +10307,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B260" t="s">
         <v>21</v>
@@ -10333,7 +10336,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B261" t="s">
         <v>21</v>
@@ -10391,13 +10394,13 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D263" t="s">
         <v>35</v>
@@ -10420,7 +10423,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B264" t="s">
         <v>21</v>
@@ -10449,7 +10452,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B265" t="s">
         <v>44</v>
@@ -10478,13 +10481,13 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B266" t="s">
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D266" t="s">
         <v>35</v>
@@ -10507,7 +10510,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B267" t="s">
         <v>21</v>
@@ -10594,7 +10597,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B270" t="s">
         <v>21</v>
@@ -10681,7 +10684,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B273" t="s">
         <v>10</v>
@@ -10710,7 +10713,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B274" t="s">
         <v>27</v>
@@ -10739,7 +10742,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B275" t="s">
         <v>21</v>
@@ -10757,10 +10760,10 @@
         <v>29</v>
       </c>
       <c r="G275" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H275" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I275">
         <v>17</v>
@@ -10797,7 +10800,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B277" t="s">
         <v>21</v>
@@ -10826,7 +10829,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B278" t="s">
         <v>21</v>
@@ -10844,10 +10847,10 @@
         <v>38</v>
       </c>
       <c r="G278" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H278" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I278">
         <v>17</v>
@@ -10942,7 +10945,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B282" t="s">
         <v>21</v>
@@ -10971,7 +10974,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B283" t="s">
         <v>10</v>
@@ -11000,7 +11003,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B284" t="s">
         <v>27</v>
@@ -11029,7 +11032,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B285" t="s">
         <v>21</v>
@@ -11047,10 +11050,10 @@
         <v>38</v>
       </c>
       <c r="G285" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H285" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I285">
         <v>18</v>
@@ -11058,7 +11061,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B286" t="s">
         <v>56</v>
@@ -11073,7 +11076,7 @@
         <v>13</v>
       </c>
       <c r="F286" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G286" t="s">
         <v>69</v>
@@ -11087,7 +11090,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B287" t="s">
         <v>21</v>
@@ -11102,7 +11105,7 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G287" t="s">
         <v>16</v>
@@ -11116,10 +11119,10 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B288" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C288" t="s">
         <v>16</v>
@@ -11174,10 +11177,10 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B290" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C290" t="s">
         <v>16</v>
@@ -11203,10 +11206,10 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B291" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C291" t="s">
         <v>16</v>
@@ -11261,7 +11264,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B293" t="s">
         <v>44</v>
@@ -11290,7 +11293,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B294" t="s">
         <v>10</v>
@@ -11348,7 +11351,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B296" t="s">
         <v>21</v>
@@ -11406,7 +11409,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B298" t="s">
         <v>86</v>
@@ -11464,7 +11467,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B300" t="s">
         <v>10</v>
@@ -11522,7 +11525,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B302" t="s">
         <v>21</v>
@@ -11580,7 +11583,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B304" t="s">
         <v>21</v>
@@ -11667,7 +11670,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B307" t="s">
         <v>21</v>
@@ -11725,7 +11728,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B309" t="s">
         <v>40</v>
@@ -11740,7 +11743,7 @@
         <v>33</v>
       </c>
       <c r="F309" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G309" t="s">
         <v>16</v>
@@ -11754,7 +11757,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B310" t="s">
         <v>56</v>
@@ -11769,7 +11772,7 @@
         <v>33</v>
       </c>
       <c r="F310" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G310" t="s">
         <v>69</v>
@@ -11783,7 +11786,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B311" t="s">
         <v>21</v>
@@ -11798,7 +11801,7 @@
         <v>33</v>
       </c>
       <c r="F311" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G311" t="s">
         <v>16</v>
@@ -11841,7 +11844,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B313" t="s">
         <v>21</v>
@@ -11870,7 +11873,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B314" t="s">
         <v>10</v>
@@ -11899,7 +11902,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B315" t="s">
         <v>56</v>
@@ -11928,7 +11931,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B316" t="s">
         <v>21</v>
@@ -11986,7 +11989,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B318" t="s">
         <v>10</v>
@@ -12044,7 +12047,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B320" t="s">
         <v>21</v>
@@ -12073,7 +12076,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B321" t="s">
         <v>21</v>
@@ -12131,10 +12134,10 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>244</v>
+      </c>
+      <c r="B323" t="s">
         <v>245</v>
-      </c>
-      <c r="B323" t="s">
-        <v>246</v>
       </c>
       <c r="C323" t="s">
         <v>16</v>
@@ -12160,7 +12163,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B324" t="s">
         <v>44</v>
@@ -12189,7 +12192,7 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B325" t="s">
         <v>10</v>
@@ -12218,7 +12221,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B326" t="s">
         <v>10</v>
@@ -12247,7 +12250,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B327" t="s">
         <v>21</v>
@@ -12276,7 +12279,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B328" t="s">
         <v>27</v>
@@ -12285,7 +12288,7 @@
         <v>28</v>
       </c>
       <c r="D328" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E328" t="s">
         <v>16</v>
@@ -12305,7 +12308,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B329" t="s">
         <v>21</v>
@@ -12320,7 +12323,7 @@
         <v>33</v>
       </c>
       <c r="F329" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G329" t="s">
         <v>16</v>
@@ -12372,7 +12375,7 @@
         <v>28</v>
       </c>
       <c r="D331" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E331" t="s">
         <v>16</v>
@@ -12392,7 +12395,7 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B332" t="s">
         <v>21</v>
@@ -12407,7 +12410,7 @@
         <v>13</v>
       </c>
       <c r="F332" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G332" t="s">
         <v>16</v>
@@ -12421,7 +12424,7 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B333" t="s">
         <v>44</v>
@@ -12479,7 +12482,7 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B335" t="s">
         <v>21</v>
@@ -12537,7 +12540,7 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B337" t="s">
         <v>10</v>
@@ -12566,7 +12569,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B338" t="s">
         <v>55</v>
@@ -12595,7 +12598,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B339" t="s">
         <v>21</v>
@@ -12682,7 +12685,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B342" t="s">
         <v>40</v>
@@ -12711,7 +12714,7 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B343" t="s">
         <v>55</v>
@@ -12740,7 +12743,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B344" t="s">
         <v>10</v>
@@ -12769,7 +12772,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B345" t="s">
         <v>86</v>
@@ -12798,7 +12801,7 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B346" t="s">
         <v>56</v>
@@ -12856,7 +12859,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B348" t="s">
         <v>10</v>
@@ -13001,7 +13004,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B353" t="s">
         <v>40</v>
@@ -13030,7 +13033,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B354" t="s">
         <v>21</v>
@@ -13059,7 +13062,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B355" t="s">
         <v>21</v>
@@ -13117,7 +13120,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B357" t="s">
         <v>40</v>
@@ -13146,7 +13149,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B358" t="s">
         <v>21</v>
@@ -13175,7 +13178,7 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B359" t="s">
         <v>10</v>
@@ -13204,7 +13207,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B360" t="s">
         <v>56</v>
@@ -13233,7 +13236,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B361" t="s">
         <v>21</v>
@@ -13291,7 +13294,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B363" t="s">
         <v>21</v>
@@ -13320,13 +13323,13 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B364" t="s">
         <v>86</v>
       </c>
       <c r="C364" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D364" t="s">
         <v>16</v>
@@ -13349,7 +13352,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B365" t="s">
         <v>25</v>
@@ -13378,7 +13381,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B366" t="s">
         <v>21</v>
@@ -13436,7 +13439,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B368" t="s">
         <v>86</v>
@@ -13465,7 +13468,7 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B369" t="s">
         <v>40</v>
@@ -13494,7 +13497,7 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B370" t="s">
         <v>18</v>
@@ -13523,7 +13526,7 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B371" t="s">
         <v>10</v>
@@ -13581,7 +13584,7 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B373" t="s">
         <v>25</v>
@@ -13610,7 +13613,7 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B374" t="s">
         <v>10</v>
@@ -13639,7 +13642,7 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B375" t="s">
         <v>21</v>
@@ -13668,7 +13671,7 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B376" t="s">
         <v>18</v>
@@ -13726,7 +13729,7 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B378" t="s">
         <v>21</v>
@@ -13755,7 +13758,7 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B379" t="s">
         <v>27</v>
@@ -13764,7 +13767,7 @@
         <v>26</v>
       </c>
       <c r="D379" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E379" t="s">
         <v>16</v>
@@ -13784,7 +13787,7 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B380" t="s">
         <v>56</v>
@@ -13799,7 +13802,7 @@
         <v>13</v>
       </c>
       <c r="F380" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G380" t="s">
         <v>69</v>
@@ -13813,7 +13816,7 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B381" t="s">
         <v>21</v>
@@ -13828,7 +13831,7 @@
         <v>13</v>
       </c>
       <c r="F381" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G381" t="s">
         <v>16</v>
@@ -13871,7 +13874,7 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B383" t="s">
         <v>10</v>
@@ -13900,7 +13903,7 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B384" t="s">
         <v>18</v>
@@ -13929,7 +13932,7 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B385" t="s">
         <v>55</v>
@@ -13958,7 +13961,7 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B386" t="s">
         <v>21</v>
@@ -14016,7 +14019,7 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B388" t="s">
         <v>40</v>
@@ -14045,7 +14048,7 @@
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B389" t="s">
         <v>10</v>
@@ -14074,7 +14077,7 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B390" t="s">
         <v>21</v>
@@ -14103,7 +14106,7 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B391" t="s">
         <v>27</v>
@@ -14132,7 +14135,7 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B392" t="s">
         <v>21</v>
@@ -14190,7 +14193,7 @@
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B394" t="s">
         <v>25</v>
@@ -14219,7 +14222,7 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B395" t="s">
         <v>25</v>
@@ -14248,7 +14251,7 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B396" t="s">
         <v>10</v>
@@ -14277,7 +14280,7 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B397" t="s">
         <v>27</v>
@@ -14306,7 +14309,7 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B398" t="s">
         <v>21</v>
@@ -14451,7 +14454,7 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B403" t="s">
         <v>40</v>
@@ -14480,7 +14483,7 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B404" t="s">
         <v>10</v>
@@ -14538,7 +14541,7 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B406" t="s">
         <v>56</v>
@@ -14596,7 +14599,7 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B408" t="s">
         <v>18</v>
@@ -14634,7 +14637,7 @@
         <v>28</v>
       </c>
       <c r="D409" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E409" t="s">
         <v>16</v>
@@ -14654,7 +14657,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B410" t="s">
         <v>21</v>
@@ -14669,7 +14672,7 @@
         <v>13</v>
       </c>
       <c r="F410" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G410" t="s">
         <v>16</v>
@@ -14683,7 +14686,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B411" t="s">
         <v>25</v>
@@ -14712,7 +14715,7 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B412" t="s">
         <v>21</v>
@@ -14727,7 +14730,7 @@
         <v>13</v>
       </c>
       <c r="F412" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G412" t="s">
         <v>16</v>
@@ -14770,7 +14773,7 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B414" t="s">
         <v>10</v>
@@ -14828,7 +14831,7 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B416" t="s">
         <v>56</v>
@@ -14843,7 +14846,7 @@
         <v>13</v>
       </c>
       <c r="F416" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G416" t="s">
         <v>69</v>
@@ -14857,7 +14860,7 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B417" t="s">
         <v>21</v>
@@ -14872,7 +14875,7 @@
         <v>13</v>
       </c>
       <c r="F417" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G417" t="s">
         <v>16</v>
@@ -14915,7 +14918,7 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B419" t="s">
         <v>21</v>
@@ -15002,7 +15005,7 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B422" t="s">
         <v>56</v>
@@ -15089,7 +15092,7 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B425" t="s">
         <v>86</v>
@@ -15118,7 +15121,7 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B426" t="s">
         <v>56</v>
@@ -15147,7 +15150,7 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B427" t="s">
         <v>21</v>
@@ -15205,7 +15208,7 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B429" t="s">
         <v>10</v>
@@ -15234,7 +15237,7 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B430" t="s">
         <v>21</v>
@@ -15263,7 +15266,7 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B431" t="s">
         <v>56</v>
@@ -15292,7 +15295,7 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B432" t="s">
         <v>21</v>
@@ -15350,7 +15353,7 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B434" t="s">
         <v>10</v>
@@ -15379,7 +15382,7 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B435" t="s">
         <v>10</v>
@@ -15388,7 +15391,7 @@
         <v>80</v>
       </c>
       <c r="D435" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E435" t="s">
         <v>15</v>
@@ -15408,7 +15411,7 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B436" t="s">
         <v>21</v>
@@ -15437,7 +15440,7 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B437" t="s">
         <v>21</v>
@@ -15524,7 +15527,7 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B440" t="s">
         <v>86</v>
@@ -15553,7 +15556,7 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -15611,7 +15614,7 @@
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B443" t="s">
         <v>10</v>
@@ -15640,13 +15643,13 @@
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B444" t="s">
         <v>55</v>
       </c>
       <c r="C444" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D444" t="s">
         <v>35</v>
@@ -15669,7 +15672,7 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B445" t="s">
         <v>21</v>
@@ -15727,7 +15730,7 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B447" t="s">
         <v>56</v>
@@ -15756,7 +15759,7 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B448" t="s">
         <v>21</v>
@@ -15814,7 +15817,7 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B450" t="s">
         <v>10</v>
@@ -15843,7 +15846,7 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B451" t="s">
         <v>25</v>
@@ -15872,7 +15875,7 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B452" t="s">
         <v>21</v>
@@ -15901,7 +15904,7 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B453" t="s">
         <v>27</v>
@@ -15930,7 +15933,7 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B454" t="s">
         <v>21</v>
@@ -15988,7 +15991,7 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B456" t="s">
         <v>25</v>
@@ -16017,7 +16020,7 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B457" t="s">
         <v>21</v>
@@ -16075,7 +16078,7 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B459" t="s">
         <v>21</v>
@@ -16104,7 +16107,7 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B460" t="s">
         <v>25</v>
@@ -16133,7 +16136,7 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B461" t="s">
         <v>21</v>
@@ -16191,7 +16194,7 @@
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B463" t="s">
         <v>56</v>
@@ -16249,7 +16252,7 @@
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B465" t="s">
         <v>18</v>
@@ -16278,7 +16281,7 @@
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B466" t="s">
         <v>21</v>
@@ -16307,13 +16310,13 @@
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B467" t="s">
         <v>40</v>
       </c>
       <c r="C467" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D467" t="s">
         <v>22</v>
@@ -16336,7 +16339,7 @@
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B468" t="s">
         <v>21</v>
@@ -16394,7 +16397,7 @@
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B470" t="s">
         <v>40</v>
@@ -16423,7 +16426,7 @@
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B471" t="s">
         <v>40</v>
@@ -16438,7 +16441,7 @@
         <v>13</v>
       </c>
       <c r="F471" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G471" t="s">
         <v>16</v>
@@ -16452,7 +16455,7 @@
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B472" t="s">
         <v>10</v>
@@ -16481,7 +16484,7 @@
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B473" t="s">
         <v>18</v>
@@ -16510,7 +16513,7 @@
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B474" t="s">
         <v>40</v>
@@ -16597,7 +16600,7 @@
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B477" t="s">
         <v>40</v>
@@ -16626,7 +16629,7 @@
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B478" t="s">
         <v>40</v>
@@ -16655,7 +16658,7 @@
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B479" t="s">
         <v>10</v>
@@ -16684,7 +16687,7 @@
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B480" t="s">
         <v>21</v>
@@ -16742,7 +16745,7 @@
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B482" t="s">
         <v>86</v>
@@ -16771,7 +16774,7 @@
     </row>
     <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B483" t="s">
         <v>21</v>
@@ -16789,10 +16792,10 @@
         <v>23</v>
       </c>
       <c r="G483" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H483" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I483">
         <v>37</v>
@@ -16800,7 +16803,7 @@
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B484" t="s">
         <v>27</v>
@@ -16829,7 +16832,7 @@
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B485" t="s">
         <v>40</v>
@@ -16858,7 +16861,7 @@
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B486" t="s">
         <v>56</v>
@@ -16887,7 +16890,7 @@
     </row>
     <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B487" t="s">
         <v>21</v>
@@ -16945,10 +16948,10 @@
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B489" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C489" t="s">
         <v>16</v>
@@ -17003,7 +17006,7 @@
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B491" t="s">
         <v>21</v>
@@ -17061,7 +17064,7 @@
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B493" t="s">
         <v>56</v>
@@ -17090,7 +17093,7 @@
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B494" t="s">
         <v>21</v>
@@ -17148,7 +17151,7 @@
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B496" t="s">
         <v>10</v>
@@ -17163,7 +17166,7 @@
         <v>33</v>
       </c>
       <c r="F496" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G496" t="s">
         <v>15</v>
@@ -17206,7 +17209,7 @@
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B498" t="s">
         <v>18</v>
@@ -17264,7 +17267,7 @@
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B500" t="s">
         <v>40</v>
@@ -17293,7 +17296,7 @@
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B501" t="s">
         <v>55</v>
@@ -17322,7 +17325,7 @@
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B502" t="s">
         <v>56</v>
@@ -17351,7 +17354,7 @@
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B503" t="s">
         <v>21</v>
@@ -17380,7 +17383,7 @@
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B504" t="s">
         <v>44</v>
@@ -17409,7 +17412,7 @@
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B505" t="s">
         <v>10</v>
@@ -17438,7 +17441,7 @@
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B506" t="s">
         <v>40</v>
@@ -17467,7 +17470,7 @@
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B507" t="s">
         <v>27</v>
@@ -17476,7 +17479,7 @@
         <v>28</v>
       </c>
       <c r="D507" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E507" t="s">
         <v>16</v>
@@ -17496,13 +17499,13 @@
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B508" t="s">
         <v>55</v>
       </c>
       <c r="C508" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D508" t="s">
         <v>22</v>
@@ -17511,7 +17514,7 @@
         <v>33</v>
       </c>
       <c r="F508" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G508" t="s">
         <v>16</v>
@@ -17525,7 +17528,7 @@
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B509" t="s">
         <v>21</v>
@@ -17540,7 +17543,7 @@
         <v>33</v>
       </c>
       <c r="F509" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G509" t="s">
         <v>16</v>
@@ -17583,7 +17586,7 @@
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B511" t="s">
         <v>25</v>
@@ -17612,7 +17615,7 @@
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B512" t="s">
         <v>10</v>
@@ -17627,7 +17630,7 @@
         <v>33</v>
       </c>
       <c r="F512" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G512" t="s">
         <v>15</v>
@@ -17650,7 +17653,7 @@
         <v>28</v>
       </c>
       <c r="D513" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E513" t="s">
         <v>16</v>
@@ -17670,7 +17673,7 @@
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B514" t="s">
         <v>21</v>
@@ -17685,7 +17688,7 @@
         <v>13</v>
       </c>
       <c r="F514" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G514" t="s">
         <v>16</v>
@@ -17728,7 +17731,7 @@
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B516" t="s">
         <v>56</v>
@@ -17757,7 +17760,7 @@
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B517" t="s">
         <v>21</v>
@@ -17786,7 +17789,7 @@
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B518" t="s">
         <v>10</v>
@@ -17801,7 +17804,7 @@
         <v>33</v>
       </c>
       <c r="F518" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G518" t="s">
         <v>52</v>
@@ -17844,7 +17847,7 @@
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B520" t="s">
         <v>56</v>
@@ -17873,7 +17876,7 @@
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B521" t="s">
         <v>21</v>
@@ -17931,7 +17934,7 @@
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B523" t="s">
         <v>27</v>
@@ -17940,7 +17943,7 @@
         <v>26</v>
       </c>
       <c r="D523" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E523" t="s">
         <v>16</v>
@@ -17960,13 +17963,13 @@
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
+        <v>380</v>
+      </c>
+      <c r="B524" t="s">
         <v>381</v>
       </c>
-      <c r="B524" t="s">
+      <c r="C524" t="s">
         <v>382</v>
-      </c>
-      <c r="C524" t="s">
-        <v>383</v>
       </c>
       <c r="D524" t="s">
         <v>22</v>
@@ -17975,7 +17978,7 @@
         <v>13</v>
       </c>
       <c r="F524" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G524" t="s">
         <v>69</v>
@@ -17989,7 +17992,7 @@
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B525" t="s">
         <v>21</v>
@@ -18004,7 +18007,7 @@
         <v>13</v>
       </c>
       <c r="F525" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G525" t="s">
         <v>16</v>
@@ -18018,7 +18021,7 @@
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B526" t="s">
         <v>10</v>
@@ -18033,7 +18036,7 @@
         <v>33</v>
       </c>
       <c r="F526" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G526" t="s">
         <v>15</v>
@@ -18047,7 +18050,7 @@
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B527" t="s">
         <v>10</v>
@@ -18056,13 +18059,13 @@
         <v>50</v>
       </c>
       <c r="D527" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E527" t="s">
         <v>33</v>
       </c>
       <c r="F527" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G527" t="s">
         <v>52</v>
@@ -18076,7 +18079,7 @@
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B528" t="s">
         <v>56</v>
@@ -18105,7 +18108,7 @@
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B529" t="s">
         <v>21</v>
@@ -18134,13 +18137,13 @@
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
+        <v>144</v>
+      </c>
+      <c r="B530" t="s">
+        <v>21</v>
+      </c>
+      <c r="C530" t="s">
         <v>145</v>
-      </c>
-      <c r="B530" t="s">
-        <v>21</v>
-      </c>
-      <c r="C530" t="s">
-        <v>146</v>
       </c>
       <c r="D530" t="s">
         <v>31</v>
@@ -18163,7 +18166,7 @@
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B531" t="s">
         <v>21</v>
@@ -18221,7 +18224,7 @@
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B533" t="s">
         <v>86</v>
@@ -18250,7 +18253,7 @@
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B534" t="s">
         <v>10</v>
@@ -18265,7 +18268,7 @@
         <v>33</v>
       </c>
       <c r="F534" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G534" t="s">
         <v>15</v>
@@ -18308,7 +18311,7 @@
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B536" t="s">
         <v>10</v>
@@ -18323,7 +18326,7 @@
         <v>33</v>
       </c>
       <c r="F536" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G536" t="s">
         <v>52</v>
@@ -18337,7 +18340,7 @@
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B537" t="s">
         <v>56</v>
@@ -18366,7 +18369,7 @@
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B538" t="s">
         <v>21</v>
@@ -18424,7 +18427,7 @@
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B540" t="s">
         <v>10</v>
@@ -18439,7 +18442,7 @@
         <v>33</v>
       </c>
       <c r="F540" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G540" t="s">
         <v>52</v>
@@ -18453,7 +18456,7 @@
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B541" t="s">
         <v>10</v>
@@ -18468,7 +18471,7 @@
         <v>33</v>
       </c>
       <c r="F541" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G541" t="s">
         <v>15</v>
@@ -18482,7 +18485,7 @@
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B542" t="s">
         <v>10</v>
@@ -18540,7 +18543,7 @@
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B544" t="s">
         <v>55</v>
@@ -18569,7 +18572,7 @@
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B545" t="s">
         <v>21</v>
@@ -18627,7 +18630,7 @@
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B547" t="s">
         <v>21</v>
@@ -18685,7 +18688,7 @@
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B549" t="s">
         <v>56</v>
@@ -18714,7 +18717,7 @@
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B550" t="s">
         <v>21</v>
@@ -18801,7 +18804,7 @@
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B553" t="s">
         <v>10</v>
@@ -18830,7 +18833,7 @@
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B554" t="s">
         <v>25</v>
@@ -18859,7 +18862,7 @@
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B555" t="s">
         <v>21</v>
@@ -18917,7 +18920,7 @@
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B557" t="s">
         <v>86</v>
@@ -18946,7 +18949,7 @@
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B558" t="s">
         <v>10</v>
@@ -18961,7 +18964,7 @@
         <v>33</v>
       </c>
       <c r="F558" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G558" t="s">
         <v>15</v>
@@ -18975,7 +18978,7 @@
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B559" t="s">
         <v>10</v>
@@ -18990,7 +18993,7 @@
         <v>33</v>
       </c>
       <c r="F559" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G559" t="s">
         <v>52</v>
@@ -19004,7 +19007,7 @@
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B560" t="s">
         <v>27</v>
@@ -19013,7 +19016,7 @@
         <v>28</v>
       </c>
       <c r="D560" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E560" t="s">
         <v>16</v>
@@ -19033,7 +19036,7 @@
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B561" t="s">
         <v>56</v>
@@ -19048,7 +19051,7 @@
         <v>13</v>
       </c>
       <c r="F561" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G561" t="s">
         <v>69</v>
@@ -19062,7 +19065,7 @@
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B562" t="s">
         <v>21</v>
@@ -19077,7 +19080,7 @@
         <v>13</v>
       </c>
       <c r="F562" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G562" t="s">
         <v>16</v>
@@ -19120,7 +19123,7 @@
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B564" t="s">
         <v>40</v>
@@ -19149,7 +19152,7 @@
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B565" t="s">
         <v>10</v>
@@ -19178,7 +19181,7 @@
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B566" t="s">
         <v>21</v>
@@ -19236,7 +19239,7 @@
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B568" t="s">
         <v>40</v>
@@ -19265,7 +19268,7 @@
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B569" t="s">
         <v>56</v>
@@ -19294,7 +19297,7 @@
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B570" t="s">
         <v>21</v>
@@ -19352,7 +19355,7 @@
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B572" t="s">
         <v>10</v>
@@ -19410,7 +19413,7 @@
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B574" t="s">
         <v>86</v>
@@ -19439,7 +19442,7 @@
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B575" t="s">
         <v>10</v>
@@ -19454,7 +19457,7 @@
         <v>33</v>
       </c>
       <c r="F575" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G575" t="s">
         <v>15</v>
@@ -19497,7 +19500,7 @@
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B577" t="s">
         <v>10</v>
@@ -19512,7 +19515,7 @@
         <v>33</v>
       </c>
       <c r="F577" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G577" t="s">
         <v>52</v>
@@ -19526,7 +19529,7 @@
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B578" t="s">
         <v>40</v>
@@ -19584,7 +19587,7 @@
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B580" t="s">
         <v>40</v>
@@ -19613,7 +19616,7 @@
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B581" t="s">
         <v>10</v>
@@ -19628,7 +19631,7 @@
         <v>33</v>
       </c>
       <c r="F581" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G581" t="s">
         <v>15</v>
@@ -19642,7 +19645,7 @@
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B582" t="s">
         <v>40</v>
@@ -19671,7 +19674,7 @@
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B583" t="s">
         <v>21</v>
@@ -19729,7 +19732,7 @@
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B585" t="s">
         <v>56</v>
@@ -19758,7 +19761,7 @@
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B586" t="s">
         <v>21</v>
@@ -19816,7 +19819,7 @@
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B588" t="s">
         <v>86</v>
@@ -19874,7 +19877,7 @@
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B590" t="s">
         <v>18</v>
@@ -19903,7 +19906,7 @@
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B591" t="s">
         <v>10</v>
@@ -19918,7 +19921,7 @@
         <v>33</v>
       </c>
       <c r="F591" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G591" t="s">
         <v>15</v>
@@ -19932,7 +19935,7 @@
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B592" t="s">
         <v>56</v>
@@ -20019,7 +20022,7 @@
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B595" t="s">
         <v>56</v>
@@ -20077,7 +20080,7 @@
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B597" t="s">
         <v>56</v>
@@ -20106,7 +20109,7 @@
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B598" t="s">
         <v>21</v>
@@ -20135,7 +20138,7 @@
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B599" t="s">
         <v>25</v>
@@ -20193,7 +20196,7 @@
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B601" t="s">
         <v>21</v>
@@ -20211,10 +20214,10 @@
         <v>29</v>
       </c>
       <c r="G601" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H601" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I601">
         <v>45</v>
@@ -20338,7 +20341,7 @@
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B606" t="s">
         <v>40</v>
@@ -20367,7 +20370,7 @@
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B607" t="s">
         <v>56</v>
@@ -20396,7 +20399,7 @@
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B608" t="s">
         <v>21</v>
@@ -20483,7 +20486,7 @@
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B611" t="s">
         <v>21</v>
@@ -20512,7 +20515,7 @@
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B612" t="s">
         <v>40</v>
@@ -20541,7 +20544,7 @@
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B613" t="s">
         <v>10</v>
@@ -20570,7 +20573,7 @@
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B614" t="s">
         <v>56</v>
@@ -20599,7 +20602,7 @@
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B615" t="s">
         <v>21</v>
@@ -20637,7 +20640,7 @@
         <v>28</v>
       </c>
       <c r="D616" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E616" t="s">
         <v>16</v>
@@ -20657,7 +20660,7 @@
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B617" t="s">
         <v>56</v>
@@ -20672,7 +20675,7 @@
         <v>33</v>
       </c>
       <c r="F617" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G617" t="s">
         <v>69</v>
@@ -20686,7 +20689,7 @@
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B618" t="s">
         <v>21</v>
@@ -20701,7 +20704,7 @@
         <v>33</v>
       </c>
       <c r="F618" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G618" t="s">
         <v>16</v>
@@ -20744,7 +20747,7 @@
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B620" t="s">
         <v>21</v>
@@ -20759,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="F620" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G620" t="s">
         <v>16</v>
@@ -20802,13 +20805,13 @@
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B622" t="s">
         <v>55</v>
       </c>
       <c r="C622" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D622" t="s">
         <v>73</v>
@@ -20831,7 +20834,7 @@
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B623" t="s">
         <v>10</v>
@@ -20846,7 +20849,7 @@
         <v>33</v>
       </c>
       <c r="F623" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G623" t="s">
         <v>15</v>
@@ -20860,7 +20863,7 @@
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B624" t="s">
         <v>21</v>
@@ -20889,7 +20892,7 @@
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B625" t="s">
         <v>86</v>
@@ -20918,7 +20921,7 @@
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B626" t="s">
         <v>10</v>
@@ -20976,7 +20979,7 @@
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B628" t="s">
         <v>86</v>
@@ -21034,7 +21037,7 @@
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B630" t="s">
         <v>10</v>
@@ -21092,7 +21095,7 @@
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B632" t="s">
         <v>56</v>
@@ -21121,7 +21124,7 @@
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B633" t="s">
         <v>21</v>
@@ -21179,7 +21182,7 @@
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B635" t="s">
         <v>18</v>
@@ -21208,13 +21211,13 @@
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B636" t="s">
         <v>55</v>
       </c>
       <c r="C636" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D636" t="s">
         <v>35</v>
@@ -21237,7 +21240,7 @@
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B637" t="s">
         <v>21</v>
@@ -21295,7 +21298,7 @@
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B639" t="s">
         <v>56</v>
@@ -21324,7 +21327,7 @@
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B640" t="s">
         <v>21</v>
@@ -21382,7 +21385,7 @@
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B642" t="s">
         <v>56</v>
@@ -21411,7 +21414,7 @@
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B643" t="s">
         <v>21</v>
@@ -21440,7 +21443,7 @@
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B644" t="s">
         <v>44</v>
@@ -21469,7 +21472,7 @@
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B645" t="s">
         <v>27</v>
@@ -21498,7 +21501,7 @@
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B646" t="s">
         <v>56</v>
@@ -21527,7 +21530,7 @@
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B647" t="s">
         <v>21</v>
@@ -21556,7 +21559,7 @@
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B648" t="s">
         <v>10</v>
@@ -21585,7 +21588,7 @@
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B649" t="s">
         <v>21</v>
@@ -21614,7 +21617,7 @@
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B650" t="s">
         <v>21</v>
@@ -21632,10 +21635,10 @@
         <v>38</v>
       </c>
       <c r="G650" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H650" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I650">
         <v>49</v>
@@ -21672,7 +21675,7 @@
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B652" t="s">
         <v>56</v>
@@ -21730,7 +21733,7 @@
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B654" t="s">
         <v>56</v>
@@ -21759,7 +21762,7 @@
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B655" t="s">
         <v>21</v>
@@ -21817,7 +21820,7 @@
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B657" t="s">
         <v>55</v>
@@ -21846,7 +21849,7 @@
     </row>
     <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B658" t="s">
         <v>21</v>
@@ -21875,7 +21878,7 @@
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B659" t="s">
         <v>10</v>
@@ -21904,7 +21907,7 @@
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B660" t="s">
         <v>40</v>
@@ -21919,7 +21922,7 @@
         <v>13</v>
       </c>
       <c r="F660" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G660" t="s">
         <v>16</v>
@@ -21933,7 +21936,7 @@
     </row>
     <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B661" t="s">
         <v>56</v>
@@ -21948,7 +21951,7 @@
         <v>13</v>
       </c>
       <c r="F661" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G661" t="s">
         <v>69</v>
@@ -21962,7 +21965,7 @@
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B662" t="s">
         <v>21</v>
@@ -21977,7 +21980,7 @@
         <v>13</v>
       </c>
       <c r="F662" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G662" t="s">
         <v>16</v>
@@ -22020,7 +22023,7 @@
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B664" t="s">
         <v>56</v>
@@ -22049,7 +22052,7 @@
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B665" t="s">
         <v>21</v>
@@ -22078,7 +22081,7 @@
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B666" t="s">
         <v>10</v>
@@ -22116,7 +22119,7 @@
         <v>28</v>
       </c>
       <c r="D667" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E667" t="s">
         <v>16</v>
@@ -22136,13 +22139,13 @@
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B668" t="s">
         <v>55</v>
       </c>
       <c r="C668" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D668" t="s">
         <v>22</v>
@@ -22151,7 +22154,7 @@
         <v>33</v>
       </c>
       <c r="F668" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G668" t="s">
         <v>16</v>
@@ -22165,7 +22168,7 @@
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B669" t="s">
         <v>55</v>
@@ -22180,7 +22183,7 @@
         <v>33</v>
       </c>
       <c r="F669" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G669" t="s">
         <v>16</v>
@@ -22194,7 +22197,7 @@
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B670" t="s">
         <v>21</v>
@@ -22209,7 +22212,7 @@
         <v>33</v>
       </c>
       <c r="F670" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G670" t="s">
         <v>16</v>
@@ -22252,7 +22255,7 @@
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B672" t="s">
         <v>21</v>
@@ -22281,7 +22284,7 @@
     </row>
     <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B673" t="s">
         <v>21</v>
@@ -22299,10 +22302,10 @@
         <v>38</v>
       </c>
       <c r="G673" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H673" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I673">
         <v>51</v>
@@ -22339,7 +22342,7 @@
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B675" t="s">
         <v>21</v>
@@ -22354,7 +22357,7 @@
         <v>13</v>
       </c>
       <c r="F675" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G675" t="s">
         <v>16</v>
@@ -22368,7 +22371,7 @@
     </row>
     <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B676" t="s">
         <v>21</v>
@@ -22386,10 +22389,10 @@
         <v>38</v>
       </c>
       <c r="G676" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H676" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I676">
         <v>52</v>
@@ -22426,7 +22429,7 @@
     </row>
     <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B678" t="s">
         <v>56</v>
@@ -22455,7 +22458,7 @@
     </row>
     <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B679" t="s">
         <v>21</v>
@@ -22513,7 +22516,7 @@
     </row>
     <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B681" t="s">
         <v>56</v>
@@ -22534,7 +22537,7 @@
         <v>69</v>
       </c>
       <c r="H681" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="I681">
         <v>52</v>
@@ -22542,7 +22545,7 @@
     </row>
     <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B682" t="s">
         <v>21</v>
@@ -22600,7 +22603,7 @@
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B684" t="s">
         <v>40</v>
@@ -22629,7 +22632,7 @@
     </row>
     <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B685" t="s">
         <v>21</v>
@@ -22658,7 +22661,7 @@
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B686" t="s">
         <v>10</v>
@@ -22687,7 +22690,7 @@
     </row>
     <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B687" t="s">
         <v>40</v>
@@ -22716,7 +22719,7 @@
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B688" t="s">
         <v>21</v>
@@ -22745,7 +22748,7 @@
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B689" t="s">
         <v>55</v>
@@ -22803,7 +22806,7 @@
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B691" t="s">
         <v>10</v>
@@ -22890,7 +22893,7 @@
     </row>
     <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B694" t="s">
         <v>27</v>
@@ -22919,13 +22922,13 @@
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B695" t="s">
         <v>55</v>
       </c>
       <c r="C695" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D695" t="s">
         <v>31</v>
@@ -22948,13 +22951,13 @@
     </row>
     <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B696" t="s">
+        <v>381</v>
+      </c>
+      <c r="C696" t="s">
         <v>382</v>
-      </c>
-      <c r="C696" t="s">
-        <v>383</v>
       </c>
       <c r="D696" t="s">
         <v>31</v>
@@ -22977,7 +22980,7 @@
     </row>
     <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B697" t="s">
         <v>21</v>
@@ -23035,7 +23038,7 @@
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B699" t="s">
         <v>40</v>
@@ -23064,7 +23067,7 @@
     </row>
     <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B700" t="s">
         <v>10</v>
@@ -23093,7 +23096,7 @@
     </row>
     <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B701" t="s">
         <v>27</v>
@@ -23102,7 +23105,7 @@
         <v>28</v>
       </c>
       <c r="D701" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E701" t="s">
         <v>16</v>
@@ -23122,7 +23125,7 @@
     </row>
     <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B702" t="s">
         <v>21</v>
@@ -23137,7 +23140,7 @@
         <v>13</v>
       </c>
       <c r="F702" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G702" t="s">
         <v>16</v>
@@ -23180,7 +23183,7 @@
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B704" t="s">
         <v>56</v>
@@ -23209,7 +23212,7 @@
     </row>
     <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B705" t="s">
         <v>21</v>
@@ -23238,7 +23241,7 @@
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B706" t="s">
         <v>56</v>
@@ -23267,7 +23270,7 @@
     </row>
     <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B707" t="s">
         <v>21</v>
@@ -23325,7 +23328,7 @@
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B709" t="s">
         <v>21</v>
@@ -23354,7 +23357,7 @@
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B710" t="s">
         <v>40</v>
@@ -23383,7 +23386,7 @@
     </row>
     <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B711" t="s">
         <v>10</v>
@@ -23412,13 +23415,13 @@
     </row>
     <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B712" t="s">
         <v>55</v>
       </c>
       <c r="C712" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D712" t="s">
         <v>22</v>
@@ -23427,7 +23430,7 @@
         <v>33</v>
       </c>
       <c r="F712" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G712" t="s">
         <v>16</v>
@@ -23441,7 +23444,7 @@
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B713" t="s">
         <v>55</v>
@@ -23456,7 +23459,7 @@
         <v>33</v>
       </c>
       <c r="F713" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G713" t="s">
         <v>16</v>
@@ -23470,7 +23473,7 @@
     </row>
     <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B714" t="s">
         <v>21</v>
@@ -23485,7 +23488,7 @@
         <v>33</v>
       </c>
       <c r="F714" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G714" t="s">
         <v>16</v>
@@ -23499,7 +23502,7 @@
     </row>
     <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B715" t="s">
         <v>21</v>
@@ -23557,7 +23560,7 @@
     </row>
     <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B717" t="s">
         <v>56</v>
@@ -23586,7 +23589,7 @@
     </row>
     <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B718" t="s">
         <v>21</v>
@@ -23644,7 +23647,7 @@
     </row>
     <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B720" t="s">
         <v>56</v>
@@ -23659,7 +23662,7 @@
         <v>13</v>
       </c>
       <c r="F720" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G720" t="s">
         <v>69</v>
@@ -23673,7 +23676,7 @@
     </row>
     <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B721" t="s">
         <v>21</v>
@@ -23688,7 +23691,7 @@
         <v>13</v>
       </c>
       <c r="F721" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G721" t="s">
         <v>16</v>
@@ -23702,7 +23705,7 @@
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B722" t="s">
         <v>40</v>
@@ -23731,7 +23734,7 @@
     </row>
     <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B723" t="s">
         <v>10</v>
@@ -23760,7 +23763,7 @@
     </row>
     <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B724" t="s">
         <v>56</v>
@@ -23789,7 +23792,7 @@
     </row>
     <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B725" t="s">
         <v>21</v>
@@ -23847,7 +23850,7 @@
     </row>
     <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B727" t="s">
         <v>40</v>
@@ -23876,7 +23879,7 @@
     </row>
     <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B728" t="s">
         <v>21</v>
@@ -23905,7 +23908,7 @@
     </row>
     <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B729" t="s">
         <v>27</v>
@@ -23934,7 +23937,7 @@
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B730" t="s">
         <v>56</v>
@@ -23963,7 +23966,7 @@
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B731" t="s">
         <v>21</v>
@@ -23992,7 +23995,7 @@
     </row>
     <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B732" t="s">
         <v>10</v>
@@ -24050,7 +24053,7 @@
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B734" t="s">
         <v>56</v>
@@ -24065,7 +24068,7 @@
         <v>33</v>
       </c>
       <c r="F734" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G734" t="s">
         <v>69</v>
@@ -24079,7 +24082,7 @@
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B735" t="s">
         <v>21</v>
@@ -24094,7 +24097,7 @@
         <v>33</v>
       </c>
       <c r="F735" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G735" t="s">
         <v>16</v>
@@ -24137,7 +24140,7 @@
     </row>
     <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B737" t="s">
         <v>27</v>
@@ -24166,7 +24169,7 @@
     </row>
     <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B738" t="s">
         <v>21</v>
@@ -24224,7 +24227,7 @@
     </row>
     <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B740" t="s">
         <v>40</v>
@@ -24253,7 +24256,7 @@
     </row>
     <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B741" t="s">
         <v>10</v>
@@ -24282,7 +24285,7 @@
     </row>
     <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B742" t="s">
         <v>21</v>
@@ -24340,7 +24343,7 @@
     </row>
     <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B744" t="s">
         <v>27</v>
@@ -24369,7 +24372,7 @@
     </row>
     <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B745" t="s">
         <v>21</v>
@@ -24427,7 +24430,7 @@
     </row>
     <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B747" t="s">
         <v>10</v>
@@ -24456,13 +24459,13 @@
     </row>
     <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B748" t="s">
         <v>55</v>
       </c>
       <c r="C748" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D748" t="s">
         <v>35</v>
@@ -24485,7 +24488,7 @@
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B749" t="s">
         <v>21</v>
@@ -24543,7 +24546,7 @@
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B751" t="s">
         <v>27</v>
@@ -24572,7 +24575,7 @@
     </row>
     <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B752" t="s">
         <v>40</v>
@@ -24601,7 +24604,7 @@
     </row>
     <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B753" t="s">
         <v>21</v>
@@ -24630,10 +24633,10 @@
     </row>
     <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B754" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C754" t="s">
         <v>16</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B756" t="s">
         <v>10</v>
@@ -24717,7 +24720,7 @@
     </row>
     <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B757" t="s">
         <v>10</v>
@@ -24804,7 +24807,7 @@
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B760" t="s">
         <v>21</v>
@@ -24862,7 +24865,7 @@
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B762" t="s">
         <v>21</v>
@@ -24920,7 +24923,7 @@
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B764" t="s">
         <v>10</v>
@@ -24978,7 +24981,7 @@
     </row>
     <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B766" t="s">
         <v>21</v>
@@ -25036,7 +25039,7 @@
     </row>
     <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B768" t="s">
         <v>86</v>
@@ -25123,7 +25126,7 @@
     </row>
     <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B771" t="s">
         <v>10</v>
@@ -25152,7 +25155,7 @@
     </row>
     <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B772" t="s">
         <v>56</v>
@@ -25210,7 +25213,7 @@
     </row>
     <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B774" t="s">
         <v>21</v>
@@ -25239,7 +25242,7 @@
     </row>
     <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B775" t="s">
         <v>21</v>
@@ -25254,7 +25257,7 @@
         <v>13</v>
       </c>
       <c r="F775" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G775" t="s">
         <v>16</v>
@@ -25268,7 +25271,7 @@
     </row>
     <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B776" t="s">
         <v>86</v>
@@ -25297,7 +25300,7 @@
     </row>
     <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B777" t="s">
         <v>10</v>
@@ -25326,7 +25329,7 @@
     </row>
     <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B778" t="s">
         <v>21</v>
@@ -25384,13 +25387,13 @@
     </row>
     <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B780" t="s">
         <v>40</v>
       </c>
       <c r="C780" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D780" t="s">
         <v>73</v>
@@ -25413,7 +25416,7 @@
     </row>
     <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B781" t="s">
         <v>56</v>
@@ -25442,7 +25445,7 @@
     </row>
     <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B782" t="s">
         <v>25</v>
@@ -25471,7 +25474,7 @@
     </row>
     <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B783" t="s">
         <v>56</v>
@@ -25500,7 +25503,7 @@
     </row>
     <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B784" t="s">
         <v>21</v>
@@ -25558,7 +25561,7 @@
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B786" t="s">
         <v>21</v>
@@ -25573,7 +25576,7 @@
         <v>33</v>
       </c>
       <c r="F786" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G786" t="s">
         <v>16</v>
@@ -25587,7 +25590,7 @@
     </row>
     <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B787" t="s">
         <v>21</v>
@@ -25616,7 +25619,7 @@
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B788" t="s">
         <v>10</v>
@@ -25645,7 +25648,7 @@
     </row>
     <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B789" t="s">
         <v>21</v>
@@ -25703,7 +25706,7 @@
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B791" t="s">
         <v>21</v>
@@ -25761,7 +25764,7 @@
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B793" t="s">
         <v>21</v>
@@ -25848,7 +25851,7 @@
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B796" t="s">
         <v>21</v>
@@ -25877,7 +25880,7 @@
     </row>
     <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B797" t="s">
         <v>18</v>
@@ -25906,7 +25909,7 @@
     </row>
     <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B798" t="s">
         <v>10</v>
@@ -25935,7 +25938,7 @@
     </row>
     <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B799" t="s">
         <v>18</v>
@@ -25964,7 +25967,7 @@
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B800" t="s">
         <v>40</v>
@@ -26022,7 +26025,7 @@
     </row>
     <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B802" t="s">
         <v>21</v>
@@ -26080,7 +26083,7 @@
     </row>
     <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B804" t="s">
         <v>21</v>
@@ -26109,7 +26112,7 @@
     </row>
     <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B805" t="s">
         <v>10</v>
@@ -26138,7 +26141,7 @@
     </row>
     <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B806" t="s">
         <v>55</v>
@@ -26167,7 +26170,7 @@
     </row>
     <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B807" t="s">
         <v>21</v>
@@ -26225,7 +26228,7 @@
     </row>
     <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B809" t="s">
         <v>40</v>
@@ -26283,7 +26286,7 @@
     </row>
     <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B811" t="s">
         <v>40</v>
@@ -26312,7 +26315,7 @@
     </row>
     <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B812" t="s">
         <v>10</v>
@@ -26399,7 +26402,7 @@
     </row>
     <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B815" t="s">
         <v>21</v>
@@ -26437,7 +26440,7 @@
         <v>28</v>
       </c>
       <c r="D816" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E816" t="s">
         <v>16</v>
@@ -26457,7 +26460,7 @@
     </row>
     <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B817" t="s">
         <v>56</v>
@@ -26472,7 +26475,7 @@
         <v>13</v>
       </c>
       <c r="F817" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G817" t="s">
         <v>69</v>
@@ -26486,7 +26489,7 @@
     </row>
     <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B818" t="s">
         <v>21</v>
@@ -26501,7 +26504,7 @@
         <v>13</v>
       </c>
       <c r="F818" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G818" t="s">
         <v>16</v>
@@ -26515,7 +26518,7 @@
     </row>
     <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B819" t="s">
         <v>56</v>
@@ -26544,7 +26547,7 @@
     </row>
     <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B820" t="s">
         <v>21</v>
@@ -26573,7 +26576,7 @@
     </row>
     <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B821" t="s">
         <v>10</v>
@@ -26602,7 +26605,7 @@
     </row>
     <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B822" t="s">
         <v>21</v>
@@ -26660,7 +26663,7 @@
     </row>
     <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B824" t="s">
         <v>21</v>
@@ -26718,7 +26721,7 @@
     </row>
     <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B826" t="s">
         <v>21</v>
@@ -26776,7 +26779,7 @@
     </row>
     <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B828" t="s">
         <v>21</v>
@@ -26791,7 +26794,7 @@
         <v>33</v>
       </c>
       <c r="F828" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G828" t="s">
         <v>16</v>
@@ -26805,7 +26808,7 @@
     </row>
     <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B829" t="s">
         <v>21</v>
@@ -26834,7 +26837,7 @@
     </row>
     <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B830" t="s">
         <v>10</v>
@@ -26892,7 +26895,7 @@
     </row>
     <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B832" t="s">
         <v>21</v>
@@ -26950,7 +26953,7 @@
     </row>
     <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B834" t="s">
         <v>21</v>
@@ -27008,7 +27011,7 @@
     </row>
     <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B836" t="s">
         <v>21</v>
@@ -27066,7 +27069,7 @@
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B838" t="s">
         <v>21</v>
@@ -27124,7 +27127,7 @@
     </row>
     <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B840" t="s">
         <v>21</v>
@@ -27153,7 +27156,7 @@
     </row>
     <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B841" t="s">
         <v>86</v>
@@ -27182,7 +27185,7 @@
     </row>
     <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B842" t="s">
         <v>10</v>
@@ -27211,7 +27214,7 @@
     </row>
     <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B843" t="s">
         <v>21</v>
@@ -27269,7 +27272,7 @@
     </row>
     <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B845" t="s">
         <v>56</v>
@@ -27298,7 +27301,7 @@
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B846" t="s">
         <v>21</v>
@@ -27327,7 +27330,7 @@
     </row>
     <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B847" t="s">
         <v>40</v>
@@ -27342,7 +27345,7 @@
         <v>33</v>
       </c>
       <c r="F847" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G847" t="s">
         <v>16</v>
@@ -27356,7 +27359,7 @@
     </row>
     <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B848" t="s">
         <v>10</v>
@@ -27385,7 +27388,7 @@
     </row>
     <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B849" t="s">
         <v>21</v>
@@ -27559,7 +27562,7 @@
     </row>
     <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B855" t="s">
         <v>10</v>
@@ -27588,7 +27591,7 @@
     </row>
     <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B856" t="s">
         <v>21</v>
@@ -27646,7 +27649,7 @@
     </row>
     <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B858" t="s">
         <v>21</v>
@@ -27704,7 +27707,7 @@
     </row>
     <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B860" t="s">
         <v>21</v>
@@ -27762,7 +27765,7 @@
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B862" t="s">
         <v>56</v>
@@ -27791,7 +27794,7 @@
     </row>
     <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B863" t="s">
         <v>21</v>
@@ -27849,7 +27852,7 @@
     </row>
     <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B865" t="s">
         <v>56</v>
@@ -27878,7 +27881,7 @@
     </row>
     <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B866" t="s">
         <v>21</v>
@@ -27936,7 +27939,7 @@
     </row>
     <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B868" t="s">
         <v>27</v>
@@ -27965,7 +27968,7 @@
     </row>
     <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B869" t="s">
         <v>21</v>
@@ -27994,7 +27997,7 @@
     </row>
     <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B870" t="s">
         <v>10</v>
@@ -28023,7 +28026,7 @@
     </row>
     <row r="871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B871" t="s">
         <v>56</v>
@@ -28052,7 +28055,7 @@
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B872" t="s">
         <v>21</v>
@@ -28110,7 +28113,7 @@
     </row>
     <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B874" t="s">
         <v>56</v>
@@ -28139,7 +28142,7 @@
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B875" t="s">
         <v>21</v>
@@ -28197,7 +28200,7 @@
     </row>
     <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B877" t="s">
         <v>86</v>
@@ -28255,7 +28258,7 @@
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B879" t="s">
         <v>21</v>
@@ -28273,10 +28276,10 @@
         <v>23</v>
       </c>
       <c r="G879" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H879" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I879">
         <v>73</v>
@@ -28284,7 +28287,7 @@
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B880" t="s">
         <v>10</v>
@@ -28342,7 +28345,7 @@
     </row>
     <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B882" t="s">
         <v>21</v>
@@ -28371,7 +28374,7 @@
     </row>
     <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B883" t="s">
         <v>21</v>
@@ -28429,7 +28432,7 @@
     </row>
     <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B885" t="s">
         <v>21</v>
@@ -28458,7 +28461,7 @@
     </row>
     <row r="886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B886" t="s">
         <v>10</v>
@@ -28487,7 +28490,7 @@
     </row>
     <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B887" t="s">
         <v>27</v>
@@ -28496,7 +28499,7 @@
         <v>26</v>
       </c>
       <c r="D887" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E887" t="s">
         <v>16</v>
@@ -28516,7 +28519,7 @@
     </row>
     <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B888" t="s">
         <v>40</v>
@@ -28531,7 +28534,7 @@
         <v>33</v>
       </c>
       <c r="F888" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G888" t="s">
         <v>16</v>
@@ -28545,7 +28548,7 @@
     </row>
     <row r="889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B889" t="s">
         <v>21</v>
@@ -28560,7 +28563,7 @@
         <v>33</v>
       </c>
       <c r="F889" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G889" t="s">
         <v>16</v>
@@ -28603,7 +28606,7 @@
     </row>
     <row r="891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B891" t="s">
         <v>40</v>
@@ -28632,7 +28635,7 @@
     </row>
     <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B892" t="s">
         <v>21</v>
@@ -28661,7 +28664,7 @@
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B893" t="s">
         <v>10</v>
@@ -28690,7 +28693,7 @@
     </row>
     <row r="894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B894" t="s">
         <v>86</v>
@@ -28748,7 +28751,7 @@
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B896" t="s">
         <v>21</v>
@@ -28777,13 +28780,13 @@
     </row>
     <row r="897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B897" t="s">
+        <v>381</v>
+      </c>
+      <c r="C897" t="s">
         <v>382</v>
-      </c>
-      <c r="C897" t="s">
-        <v>383</v>
       </c>
       <c r="D897" t="s">
         <v>31</v>
@@ -28806,7 +28809,7 @@
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B898" t="s">
         <v>21</v>
@@ -28864,7 +28867,7 @@
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B900" t="s">
         <v>86</v>
@@ -28922,7 +28925,7 @@
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B902" t="s">
         <v>10</v>
@@ -28951,7 +28954,7 @@
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B903" t="s">
         <v>56</v>
@@ -28980,7 +28983,7 @@
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B904" t="s">
         <v>21</v>
@@ -29009,7 +29012,7 @@
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B905" t="s">
         <v>21</v>
@@ -29067,7 +29070,7 @@
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B907" t="s">
         <v>21</v>
@@ -29096,7 +29099,7 @@
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B908" t="s">
         <v>21</v>
@@ -29154,7 +29157,7 @@
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B910" t="s">
         <v>21</v>
@@ -29183,7 +29186,7 @@
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B911" t="s">
         <v>56</v>
@@ -29212,7 +29215,7 @@
     </row>
     <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B912" t="s">
         <v>21</v>
@@ -29270,7 +29273,7 @@
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B914" t="s">
         <v>56</v>
@@ -29285,7 +29288,7 @@
         <v>13</v>
       </c>
       <c r="F914" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G914" t="s">
         <v>69</v>
@@ -29299,7 +29302,7 @@
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B915" t="s">
         <v>56</v>
@@ -29314,7 +29317,7 @@
         <v>13</v>
       </c>
       <c r="F915" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G915" t="s">
         <v>69</v>
@@ -29328,7 +29331,7 @@
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B916" t="s">
         <v>21</v>
@@ -29343,7 +29346,7 @@
         <v>13</v>
       </c>
       <c r="F916" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G916" t="s">
         <v>16</v>
@@ -29386,7 +29389,7 @@
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B918" t="s">
         <v>27</v>
@@ -29415,7 +29418,7 @@
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B919" t="s">
         <v>21</v>
@@ -29444,7 +29447,7 @@
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B920" t="s">
         <v>86</v>
@@ -29473,7 +29476,7 @@
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B921" t="s">
         <v>10</v>
@@ -29502,7 +29505,7 @@
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B922" t="s">
         <v>21</v>
@@ -29531,7 +29534,7 @@
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B923" t="s">
         <v>56</v>
@@ -29560,7 +29563,7 @@
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B924" t="s">
         <v>21</v>
@@ -29647,7 +29650,7 @@
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B927" t="s">
         <v>21</v>
@@ -29705,7 +29708,7 @@
     </row>
     <row r="929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B929" t="s">
         <v>56</v>
@@ -29734,7 +29737,7 @@
     </row>
     <row r="930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B930" t="s">
         <v>21</v>
@@ -29792,7 +29795,7 @@
     </row>
     <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B932" t="s">
         <v>21</v>
@@ -29821,7 +29824,7 @@
     </row>
     <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B933" t="s">
         <v>10</v>
@@ -29879,7 +29882,7 @@
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B935" t="s">
         <v>21</v>
@@ -29897,10 +29900,10 @@
         <v>23</v>
       </c>
       <c r="G935" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H935" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I935">
         <v>79</v>
@@ -29937,7 +29940,7 @@
     </row>
     <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B937" t="s">
         <v>56</v>
@@ -29966,7 +29969,7 @@
     </row>
     <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B938" t="s">
         <v>21</v>
@@ -29995,7 +29998,7 @@
     </row>
     <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B939" t="s">
         <v>40</v>
@@ -30024,7 +30027,7 @@
     </row>
     <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B940" t="s">
         <v>21</v>
@@ -30082,7 +30085,7 @@
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B942" t="s">
         <v>56</v>
@@ -30111,7 +30114,7 @@
     </row>
     <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B943" t="s">
         <v>21</v>
@@ -30169,7 +30172,7 @@
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B945" t="s">
         <v>21</v>
@@ -30227,7 +30230,7 @@
     </row>
     <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B947" t="s">
         <v>21</v>
@@ -30256,7 +30259,7 @@
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B948" t="s">
         <v>10</v>
@@ -30285,13 +30288,13 @@
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B949" t="s">
+        <v>381</v>
+      </c>
+      <c r="C949" t="s">
         <v>382</v>
-      </c>
-      <c r="C949" t="s">
-        <v>383</v>
       </c>
       <c r="D949" t="s">
         <v>73</v>
@@ -30343,7 +30346,7 @@
     </row>
     <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B951" t="s">
         <v>56</v>
@@ -30372,7 +30375,7 @@
     </row>
     <row r="952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B952" t="s">
         <v>21</v>
@@ -30430,7 +30433,7 @@
     </row>
     <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B954" t="s">
         <v>27</v>
@@ -30459,7 +30462,7 @@
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B955" t="s">
         <v>21</v>
@@ -30488,7 +30491,7 @@
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B956" t="s">
         <v>40</v>
@@ -30517,7 +30520,7 @@
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B957" t="s">
         <v>10</v>
@@ -30546,7 +30549,7 @@
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B958" t="s">
         <v>21</v>
@@ -30633,7 +30636,7 @@
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B961" t="s">
         <v>21</v>
@@ -30662,7 +30665,7 @@
     </row>
     <row r="962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B962" t="s">
         <v>21</v>
@@ -30720,7 +30723,7 @@
     </row>
     <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B964" t="s">
         <v>10</v>
@@ -30749,7 +30752,7 @@
     </row>
     <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B965" t="s">
         <v>56</v>
@@ -30778,7 +30781,7 @@
     </row>
     <row r="966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B966" t="s">
         <v>21</v>
@@ -30836,7 +30839,7 @@
     </row>
     <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B968" t="s">
         <v>40</v>
@@ -30865,7 +30868,7 @@
     </row>
     <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B969" t="s">
         <v>21</v>
@@ -30894,13 +30897,13 @@
     </row>
     <row r="970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B970" t="s">
         <v>56</v>
       </c>
       <c r="C970" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D970" t="s">
         <v>73</v>
@@ -30923,7 +30926,7 @@
     </row>
     <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B971" t="s">
         <v>10</v>
@@ -31010,7 +31013,7 @@
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B974" t="s">
         <v>21</v>
@@ -31039,7 +31042,7 @@
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B975" t="s">
         <v>10</v>
@@ -31068,7 +31071,7 @@
     </row>
     <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B976" t="s">
         <v>56</v>
@@ -31097,7 +31100,7 @@
     </row>
     <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B977" t="s">
         <v>21</v>
@@ -31126,7 +31129,7 @@
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B978" t="s">
         <v>27</v>
@@ -31155,7 +31158,7 @@
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B979" t="s">
         <v>21</v>
@@ -31213,7 +31216,7 @@
     </row>
     <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B981" t="s">
         <v>40</v>
@@ -31242,7 +31245,7 @@
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B982" t="s">
         <v>56</v>
@@ -31271,7 +31274,7 @@
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B983" t="s">
         <v>21</v>
@@ -31329,7 +31332,7 @@
     </row>
     <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B985" t="s">
         <v>10</v>
@@ -31358,7 +31361,7 @@
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B986" t="s">
         <v>56</v>
@@ -31373,7 +31376,7 @@
         <v>13</v>
       </c>
       <c r="F986" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G986" t="s">
         <v>69</v>
@@ -31387,7 +31390,7 @@
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B987" t="s">
         <v>21</v>
@@ -31402,7 +31405,7 @@
         <v>13</v>
       </c>
       <c r="F987" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G987" t="s">
         <v>16</v>
@@ -31474,7 +31477,7 @@
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B990" t="s">
         <v>21</v>
@@ -31532,7 +31535,7 @@
     </row>
     <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B992" t="s">
         <v>10</v>
@@ -31561,7 +31564,7 @@
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B993" t="s">
         <v>18</v>
@@ -31590,7 +31593,7 @@
     </row>
     <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B994" t="s">
         <v>56</v>
@@ -31619,7 +31622,7 @@
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B995" t="s">
         <v>21</v>
@@ -31677,7 +31680,7 @@
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B997" t="s">
         <v>56</v>
@@ -31706,7 +31709,7 @@
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B998" t="s">
         <v>21</v>
@@ -31735,7 +31738,7 @@
     </row>
     <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B999" t="s">
         <v>10</v>
@@ -31764,7 +31767,7 @@
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B1000" t="s">
         <v>56</v>
@@ -31793,7 +31796,7 @@
     </row>
     <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B1001" t="s">
         <v>21</v>
@@ -31851,7 +31854,7 @@
     </row>
     <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1003" t="s">
         <v>56</v>
@@ -31880,7 +31883,7 @@
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B1004" t="s">
         <v>21</v>
@@ -31909,7 +31912,7 @@
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B1005" t="s">
         <v>10</v>
@@ -31938,7 +31941,7 @@
     </row>
     <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1006" t="s">
         <v>56</v>
@@ -31967,7 +31970,7 @@
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B1007" t="s">
         <v>21</v>
@@ -31996,13 +31999,13 @@
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B1008" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1008" t="s">
         <v>382</v>
-      </c>
-      <c r="C1008" t="s">
-        <v>383</v>
       </c>
       <c r="D1008" t="s">
         <v>31</v>
@@ -32054,7 +32057,7 @@
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B1010" t="s">
         <v>21</v>
@@ -32141,7 +32144,7 @@
     </row>
     <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B1013" t="s">
         <v>21</v>
@@ -32170,7 +32173,7 @@
     </row>
     <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1014" t="s">
         <v>21</v>
@@ -32199,7 +32202,7 @@
     </row>
     <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B1015" t="s">
         <v>10</v>
@@ -32228,7 +32231,7 @@
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B1016" t="s">
         <v>21</v>
@@ -32257,7 +32260,7 @@
     </row>
     <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B1017" t="s">
         <v>56</v>
@@ -32286,7 +32289,7 @@
     </row>
     <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1018" t="s">
         <v>21</v>
@@ -32344,7 +32347,7 @@
     </row>
     <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B1020" t="s">
         <v>56</v>
@@ -32373,7 +32376,7 @@
     </row>
     <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1021" t="s">
         <v>21</v>
@@ -32402,7 +32405,7 @@
     </row>
     <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B1022" t="s">
         <v>21</v>
@@ -32431,7 +32434,7 @@
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B1023" t="s">
         <v>25</v>
@@ -32460,7 +32463,7 @@
     </row>
     <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1024" t="s">
         <v>10</v>
@@ -32518,7 +32521,7 @@
     </row>
     <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B1026" t="s">
         <v>25</v>
@@ -32547,7 +32550,7 @@
     </row>
     <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1027" t="s">
         <v>86</v>
@@ -32576,7 +32579,7 @@
     </row>
     <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B1028" t="s">
         <v>10</v>
@@ -32605,7 +32608,7 @@
     </row>
     <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B1029" t="s">
         <v>18</v>
@@ -32634,7 +32637,7 @@
     </row>
     <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1030" t="s">
         <v>27</v>
@@ -32663,13 +32666,13 @@
     </row>
     <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B1031" t="s">
         <v>40</v>
       </c>
       <c r="C1031" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1031" t="s">
         <v>22</v>
@@ -32692,7 +32695,7 @@
     </row>
     <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B1032" t="s">
         <v>21</v>
@@ -32750,7 +32753,7 @@
     </row>
     <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1034" t="s">
         <v>21</v>
@@ -32837,7 +32840,7 @@
     </row>
     <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B1037" t="s">
         <v>21</v>
@@ -32855,10 +32858,10 @@
         <v>29</v>
       </c>
       <c r="G1037" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H1037" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I1037">
         <v>88</v>
@@ -32895,7 +32898,7 @@
     </row>
     <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B1039" t="s">
         <v>86</v>
@@ -32924,7 +32927,7 @@
     </row>
     <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1040" t="s">
         <v>10</v>
@@ -32982,7 +32985,7 @@
     </row>
     <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B1042" t="s">
         <v>10</v>
@@ -33040,7 +33043,7 @@
     </row>
     <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1044" t="s">
         <v>27</v>
@@ -33069,7 +33072,7 @@
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1045" t="s">
         <v>56</v>
@@ -33098,7 +33101,7 @@
     </row>
     <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B1046" t="s">
         <v>21</v>
@@ -33127,7 +33130,7 @@
     </row>
     <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B1047" t="s">
         <v>10</v>
@@ -33156,7 +33159,7 @@
     </row>
     <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B1048" t="s">
         <v>56</v>
@@ -33185,7 +33188,7 @@
     </row>
     <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1049" t="s">
         <v>21</v>
@@ -33243,7 +33246,7 @@
     </row>
     <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1051" t="s">
         <v>56</v>
@@ -33272,7 +33275,7 @@
     </row>
     <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B1052" t="s">
         <v>21</v>
@@ -33359,7 +33362,7 @@
     </row>
     <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B1055" t="s">
         <v>56</v>
@@ -33388,7 +33391,7 @@
     </row>
     <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B1056" t="s">
         <v>21</v>
@@ -33446,7 +33449,7 @@
     </row>
     <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1058" t="s">
         <v>27</v>
@@ -33455,7 +33458,7 @@
         <v>28</v>
       </c>
       <c r="D1058" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E1058" t="s">
         <v>16</v>
@@ -33475,7 +33478,7 @@
     </row>
     <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B1059" t="s">
         <v>40</v>
@@ -33490,7 +33493,7 @@
         <v>13</v>
       </c>
       <c r="F1059" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G1059" t="s">
         <v>16</v>
@@ -33504,7 +33507,7 @@
     </row>
     <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B1060" t="s">
         <v>21</v>
@@ -33519,7 +33522,7 @@
         <v>33</v>
       </c>
       <c r="F1060" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G1060" t="s">
         <v>16</v>
@@ -33533,7 +33536,7 @@
     </row>
     <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B1061" t="s">
         <v>10</v>
@@ -33591,7 +33594,7 @@
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1063" t="s">
         <v>56</v>
@@ -33620,7 +33623,7 @@
     </row>
     <row r="1064" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B1064" t="s">
         <v>21</v>
@@ -33649,7 +33652,7 @@
     </row>
     <row r="1065" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1065" t="s">
         <v>40</v>
@@ -33664,7 +33667,7 @@
         <v>13</v>
       </c>
       <c r="F1065" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G1065" t="s">
         <v>16</v>
@@ -33678,7 +33681,7 @@
     </row>
     <row r="1066" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B1066" t="s">
         <v>21</v>
@@ -33693,7 +33696,7 @@
         <v>13</v>
       </c>
       <c r="F1066" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G1066" t="s">
         <v>16</v>
@@ -33736,7 +33739,7 @@
     </row>
     <row r="1068" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1068" t="s">
         <v>10</v>
@@ -33765,7 +33768,7 @@
     </row>
     <row r="1069" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B1069" t="s">
         <v>21</v>
@@ -33794,7 +33797,7 @@
     </row>
     <row r="1070" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B1070" t="s">
         <v>86</v>
@@ -33823,7 +33826,7 @@
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B1071" t="s">
         <v>56</v>
@@ -33852,7 +33855,7 @@
     </row>
     <row r="1072" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1072" t="s">
         <v>21</v>
@@ -33881,7 +33884,7 @@
     </row>
     <row r="1073" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B1073" t="s">
         <v>21</v>
@@ -33968,7 +33971,7 @@
     </row>
     <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B1076" t="s">
         <v>40</v>
@@ -33983,7 +33986,7 @@
         <v>13</v>
       </c>
       <c r="F1076" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G1076" t="s">
         <v>16</v>
@@ -33997,7 +34000,7 @@
     </row>
     <row r="1077" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1077" t="s">
         <v>10</v>
@@ -34026,7 +34029,7 @@
     </row>
     <row r="1078" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1078" t="s">
         <v>27</v>
@@ -34035,7 +34038,7 @@
         <v>28</v>
       </c>
       <c r="D1078" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E1078" t="s">
         <v>16</v>
@@ -34055,7 +34058,7 @@
     </row>
     <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B1079" t="s">
         <v>21</v>
@@ -34070,7 +34073,7 @@
         <v>13</v>
       </c>
       <c r="F1079" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G1079" t="s">
         <v>16</v>
@@ -34084,7 +34087,7 @@
     </row>
     <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1080" t="s">
         <v>56</v>
@@ -34113,7 +34116,7 @@
     </row>
     <row r="1081" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B1081" t="s">
         <v>21</v>
@@ -34171,7 +34174,7 @@
     </row>
     <row r="1083" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B1083" t="s">
         <v>21</v>
@@ -34200,7 +34203,7 @@
     </row>
     <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1084" t="s">
         <v>10</v>
@@ -34229,7 +34232,7 @@
     </row>
     <row r="1085" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B1085" t="s">
         <v>21</v>
@@ -34258,7 +34261,7 @@
     </row>
     <row r="1086" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1086" t="s">
         <v>27</v>
@@ -34287,7 +34290,7 @@
     </row>
     <row r="1087" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B1087" t="s">
         <v>56</v>
@@ -34316,7 +34319,7 @@
     </row>
     <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B1088" t="s">
         <v>21</v>
@@ -34345,7 +34348,7 @@
     </row>
     <row r="1089" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1089" t="s">
         <v>21</v>
@@ -34403,7 +34406,7 @@
     </row>
     <row r="1091" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B1091" t="s">
         <v>21</v>
@@ -34461,7 +34464,7 @@
     </row>
     <row r="1093" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1093" t="s">
         <v>27</v>
@@ -34490,7 +34493,7 @@
     </row>
     <row r="1094" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B1094" t="s">
         <v>21</v>
@@ -34519,7 +34522,7 @@
     </row>
     <row r="1095" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1095" t="s">
         <v>21</v>
@@ -34577,7 +34580,7 @@
     </row>
     <row r="1097" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1097" t="s">
         <v>21</v>
@@ -34664,7 +34667,7 @@
     </row>
     <row r="1100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B1100" t="s">
         <v>21</v>
@@ -34751,7 +34754,7 @@
     </row>
     <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B1103" t="s">
         <v>56</v>
@@ -34780,7 +34783,7 @@
     </row>
     <row r="1104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B1104" t="s">
         <v>56</v>
@@ -34809,7 +34812,7 @@
     </row>
     <row r="1105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B1105" t="s">
         <v>21</v>
@@ -34838,7 +34841,7 @@
     </row>
     <row r="1106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1106" t="s">
         <v>27</v>
@@ -34867,7 +34870,7 @@
     </row>
     <row r="1107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B1107" t="s">
         <v>21</v>
@@ -34896,7 +34899,7 @@
     </row>
     <row r="1108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B1108" t="s">
         <v>10</v>
@@ -34925,7 +34928,7 @@
     </row>
     <row r="1109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B1109" t="s">
         <v>18</v>
@@ -34954,13 +34957,13 @@
     </row>
     <row r="1110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B1110" t="s">
         <v>55</v>
       </c>
       <c r="C1110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1110" t="s">
         <v>35</v>
@@ -35012,13 +35015,13 @@
     </row>
     <row r="1112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B1112" t="s">
         <v>40</v>
       </c>
       <c r="C1112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1112" t="s">
         <v>22</v>
@@ -35041,7 +35044,7 @@
     </row>
     <row r="1113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B1113" t="s">
         <v>21</v>
@@ -35070,7 +35073,7 @@
     </row>
     <row r="1114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B1114" t="s">
         <v>10</v>
@@ -35099,7 +35102,7 @@
     </row>
     <row r="1115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B1115" t="s">
         <v>18</v>
@@ -35157,10 +35160,10 @@
     </row>
     <row r="1117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B1117" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C1117" t="s">
         <v>16</v>
@@ -35215,7 +35218,7 @@
     </row>
     <row r="1119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B1119" t="s">
         <v>44</v>
@@ -35244,7 +35247,7 @@
     </row>
     <row r="1120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B1120" t="s">
         <v>55</v>
@@ -35273,7 +35276,7 @@
     </row>
     <row r="1121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B1121" t="s">
         <v>44</v>
@@ -35302,7 +35305,7 @@
     </row>
     <row r="1122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B1122" t="s">
         <v>21</v>
@@ -35360,7 +35363,7 @@
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B1124" t="s">
         <v>21</v>
@@ -35418,7 +35421,7 @@
     </row>
     <row r="1126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B1126" t="s">
         <v>40</v>
@@ -35447,7 +35450,7 @@
     </row>
     <row r="1127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B1127" t="s">
         <v>10</v>
@@ -35476,7 +35479,7 @@
     </row>
     <row r="1128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B1128" t="s">
         <v>18</v>
@@ -35505,7 +35508,7 @@
     </row>
     <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B1129" t="s">
         <v>21</v>
@@ -35563,7 +35566,7 @@
     </row>
     <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B1131" t="s">
         <v>21</v>
@@ -35621,7 +35624,7 @@
     </row>
     <row r="1133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B1133" t="s">
         <v>56</v>
@@ -35650,7 +35653,7 @@
     </row>
     <row r="1134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B1134" t="s">
         <v>21</v>
@@ -35708,7 +35711,7 @@
     </row>
     <row r="1136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1136" t="s">
         <v>27</v>
@@ -35737,7 +35740,7 @@
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B1137" t="s">
         <v>40</v>
@@ -35766,7 +35769,7 @@
     </row>
     <row r="1138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B1138" t="s">
         <v>21</v>
@@ -35795,7 +35798,7 @@
     </row>
     <row r="1139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B1139" t="s">
         <v>21</v>
@@ -35813,10 +35816,10 @@
         <v>38</v>
       </c>
       <c r="G1139" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H1139" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I1139">
         <v>96</v>
@@ -35853,7 +35856,7 @@
     </row>
     <row r="1141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B1141" t="s">
         <v>10</v>
@@ -35882,7 +35885,7 @@
     </row>
     <row r="1142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B1142" t="s">
         <v>56</v>
@@ -35911,7 +35914,7 @@
     </row>
     <row r="1143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B1143" t="s">
         <v>21</v>
@@ -35998,7 +36001,7 @@
     </row>
     <row r="1146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B1146" t="s">
         <v>40</v>
@@ -36027,7 +36030,7 @@
     </row>
     <row r="1147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1147" t="s">
         <v>10</v>
@@ -36056,13 +36059,13 @@
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B1148" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1148" t="s">
         <v>382</v>
-      </c>
-      <c r="C1148" t="s">
-        <v>383</v>
       </c>
       <c r="D1148" t="s">
         <v>22</v>
@@ -36085,7 +36088,7 @@
     </row>
     <row r="1149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B1149" t="s">
         <v>21</v>
@@ -36143,7 +36146,7 @@
     </row>
     <row r="1151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B1151" t="s">
         <v>21</v>
@@ -36201,7 +36204,7 @@
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B1153" t="s">
         <v>21</v>
@@ -36259,7 +36262,7 @@
     </row>
     <row r="1155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B1155" t="s">
         <v>21</v>
@@ -36317,7 +36320,7 @@
     </row>
     <row r="1157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B1157" t="s">
         <v>21</v>
@@ -36375,7 +36378,7 @@
     </row>
     <row r="1159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1159" t="s">
         <v>27</v>
@@ -36404,10 +36407,10 @@
     </row>
     <row r="1160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B1160" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C1160" t="s">
         <v>16</v>
@@ -36462,7 +36465,7 @@
     </row>
     <row r="1162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B1162" t="s">
         <v>44</v>
@@ -36491,7 +36494,7 @@
     </row>
     <row r="1163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1163" t="s">
         <v>55</v>
@@ -36520,7 +36523,7 @@
     </row>
     <row r="1164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B1164" t="s">
         <v>44</v>
@@ -36549,7 +36552,7 @@
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B1165" t="s">
         <v>21</v>
@@ -36607,7 +36610,7 @@
     </row>
     <row r="1167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B1167" t="s">
         <v>27</v>
@@ -36636,7 +36639,7 @@
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B1168" t="s">
         <v>21</v>
@@ -36665,7 +36668,7 @@
     </row>
     <row r="1169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B1169" t="s">
         <v>10</v>
@@ -36694,7 +36697,7 @@
     </row>
     <row r="1170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B1170" t="s">
         <v>10</v>
@@ -36723,7 +36726,7 @@
     </row>
     <row r="1171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B1171" t="s">
         <v>56</v>
@@ -36752,7 +36755,7 @@
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B1172" t="s">
         <v>21</v>
@@ -36781,7 +36784,7 @@
     </row>
     <row r="1173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B1173" t="s">
         <v>27</v>
@@ -36810,7 +36813,7 @@
     </row>
     <row r="1174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B1174" t="s">
         <v>21</v>
@@ -36868,7 +36871,7 @@
     </row>
     <row r="1176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B1176" t="s">
         <v>21</v>
@@ -36897,7 +36900,7 @@
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B1177" t="s">
         <v>10</v>
@@ -36955,7 +36958,7 @@
     </row>
     <row r="1179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B1179" t="s">
         <v>21</v>
@@ -36984,7 +36987,7 @@
     </row>
     <row r="1180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B1180" t="s">
         <v>10</v>
@@ -37013,7 +37016,7 @@
     </row>
     <row r="1181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B1181" t="s">
         <v>56</v>
@@ -37042,7 +37045,7 @@
     </row>
     <row r="1182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B1182" t="s">
         <v>21</v>
@@ -37071,7 +37074,7 @@
     </row>
     <row r="1183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B1183" t="s">
         <v>21</v>
@@ -37129,7 +37132,7 @@
     </row>
     <row r="1185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B1185" t="s">
         <v>10</v>
@@ -37158,7 +37161,7 @@
     </row>
     <row r="1186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1186" t="s">
         <v>27</v>
@@ -37167,7 +37170,7 @@
         <v>28</v>
       </c>
       <c r="D1186" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E1186" t="s">
         <v>16</v>
@@ -37187,7 +37190,7 @@
     </row>
     <row r="1187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B1187" t="s">
         <v>40</v>
@@ -37202,7 +37205,7 @@
         <v>13</v>
       </c>
       <c r="F1187" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G1187" t="s">
         <v>16</v>
@@ -37245,7 +37248,7 @@
     </row>
     <row r="1189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B1189" t="s">
         <v>21</v>
@@ -37274,7 +37277,7 @@
     </row>
     <row r="1190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B1190" t="s">
         <v>21</v>
@@ -37332,7 +37335,7 @@
     </row>
     <row r="1192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B1192" t="s">
         <v>56</v>
@@ -37361,7 +37364,7 @@
     </row>
     <row r="1193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B1193" t="s">
         <v>56</v>
@@ -37390,7 +37393,7 @@
     </row>
     <row r="1194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B1194" t="s">
         <v>21</v>
@@ -37448,7 +37451,7 @@
     </row>
     <row r="1196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B1196" t="s">
         <v>21</v>
@@ -37466,10 +37469,10 @@
         <v>29</v>
       </c>
       <c r="G1196" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H1196" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I1196">
         <v>100</v>
@@ -37535,7 +37538,7 @@
     </row>
     <row r="1199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B1199" t="s">
         <v>21</v>
@@ -37553,10 +37556,10 @@
         <v>29</v>
       </c>
       <c r="G1199" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="H1199" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="I1199">
         <v>100</v>
@@ -37592,6 +37595,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1200" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>